--- a/public/exports-60-250-with-coowners/29189889.xlsx
+++ b/public/exports-60-250-with-coowners/29189889.xlsx
@@ -8104,12 +8104,12 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8179,12 +8179,12 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
